--- a/CARGO_ARRIVAL_NIGHT.xlsx
+++ b/CARGO_ARRIVAL_NIGHT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fiona\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fiona\optimisation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668D8975-258B-4A82-8EEA-DA701A65780A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED996F-1EDF-482C-8920-3CAA1CCAE60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4C96D902-8C59-4966-B0F7-AE5ADA9D8A6E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="7" xr2:uid="{4C96D902-8C59-4966-B0F7-AE5ADA9D8A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="40">
   <si>
     <t>Night</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>Acar6</t>
-  </si>
-  <si>
-    <t>ALSC</t>
   </si>
 </sst>
 </file>
@@ -625,15 +622,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -646,14 +634,23 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="403">
+  <dxfs count="112">
     <dxf>
       <fill>
         <patternFill>
@@ -735,6 +732,13 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -825,7 +829,84 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -923,84 +1004,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1078,286 +1082,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1449,97 +1173,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1799,1679 +1432,6 @@
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3960,203 +1920,203 @@
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41">
+      <c r="B1" s="38">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C1" s="42">
+      <c r="C1" s="39">
         <v>0.92708333333333337</v>
       </c>
-      <c r="D1" s="42">
+      <c r="D1" s="39">
         <v>0.9375</v>
       </c>
-      <c r="E1" s="43">
+      <c r="E1" s="40">
         <v>0.94791666666666663</v>
       </c>
-      <c r="F1" s="41">
+      <c r="F1" s="38">
         <v>0.95833333333333404</v>
       </c>
-      <c r="G1" s="42">
+      <c r="G1" s="39">
         <v>0.96875</v>
       </c>
-      <c r="H1" s="42">
+      <c r="H1" s="39">
         <v>0.97916666666666696</v>
       </c>
-      <c r="I1" s="43">
+      <c r="I1" s="40">
         <v>0.98958333333333404</v>
       </c>
-      <c r="J1" s="41">
+      <c r="J1" s="38">
         <v>1</v>
       </c>
-      <c r="K1" s="42">
+      <c r="K1" s="39">
         <v>1.0104166666666701</v>
       </c>
-      <c r="L1" s="42">
+      <c r="L1" s="39">
         <v>1.0208333333333299</v>
       </c>
-      <c r="M1" s="43">
+      <c r="M1" s="40">
         <v>1.03125</v>
       </c>
-      <c r="N1" s="41">
+      <c r="N1" s="38">
         <v>1.0416666666666701</v>
       </c>
-      <c r="O1" s="42">
+      <c r="O1" s="39">
         <v>1.0520833333333299</v>
       </c>
-      <c r="P1" s="42">
+      <c r="P1" s="39">
         <v>1.0625</v>
       </c>
-      <c r="Q1" s="43">
+      <c r="Q1" s="40">
         <v>1.0729166666666701</v>
       </c>
-      <c r="R1" s="41">
+      <c r="R1" s="38">
         <v>1.0833333333333299</v>
       </c>
-      <c r="S1" s="42">
+      <c r="S1" s="39">
         <v>1.09375</v>
       </c>
-      <c r="T1" s="42">
+      <c r="T1" s="39">
         <v>1.1041666666666701</v>
       </c>
-      <c r="U1" s="43">
+      <c r="U1" s="40">
         <v>1.1145833333333299</v>
       </c>
-      <c r="V1" s="41">
+      <c r="V1" s="38">
         <v>1.125</v>
       </c>
-      <c r="W1" s="42">
+      <c r="W1" s="39">
         <v>1.1354166666666701</v>
       </c>
-      <c r="X1" s="42">
+      <c r="X1" s="39">
         <v>1.1458333333333299</v>
       </c>
-      <c r="Y1" s="43">
+      <c r="Y1" s="40">
         <v>1.15625</v>
       </c>
-      <c r="Z1" s="41">
+      <c r="Z1" s="38">
         <v>1.1666666666666701</v>
       </c>
-      <c r="AA1" s="42">
+      <c r="AA1" s="39">
         <v>1.1770833333333399</v>
       </c>
-      <c r="AB1" s="42">
+      <c r="AB1" s="39">
         <v>1.1875</v>
       </c>
-      <c r="AC1" s="43">
+      <c r="AC1" s="40">
         <v>1.1979166666666701</v>
       </c>
-      <c r="AD1" s="41">
+      <c r="AD1" s="38">
         <v>1.2083333333333399</v>
       </c>
-      <c r="AE1" s="42">
+      <c r="AE1" s="39">
         <v>1.21875</v>
       </c>
-      <c r="AF1" s="42">
+      <c r="AF1" s="39">
         <v>1.2291666666666701</v>
       </c>
-      <c r="AG1" s="43">
+      <c r="AG1" s="40">
         <v>1.2395833333333399</v>
       </c>
-      <c r="AH1" s="41">
+      <c r="AH1" s="38">
         <v>1.25</v>
       </c>
-      <c r="AI1" s="42">
+      <c r="AI1" s="39">
         <v>1.2604166666666701</v>
       </c>
-      <c r="AJ1" s="42">
+      <c r="AJ1" s="39">
         <v>1.2708333333333399</v>
       </c>
-      <c r="AK1" s="43">
+      <c r="AK1" s="40">
         <v>1.28125</v>
       </c>
-      <c r="AL1" s="41">
+      <c r="AL1" s="38">
         <v>1.2916666666666701</v>
       </c>
-      <c r="AM1" s="42">
+      <c r="AM1" s="39">
         <v>1.3020833333333399</v>
       </c>
-      <c r="AN1" s="42">
+      <c r="AN1" s="39">
         <v>1.3125</v>
       </c>
-      <c r="AO1" s="43">
+      <c r="AO1" s="40">
         <v>1.3229166666666701</v>
       </c>
-      <c r="AP1" s="41">
+      <c r="AP1" s="38">
         <v>1.3333333333333399</v>
       </c>
-      <c r="AQ1" s="42">
+      <c r="AQ1" s="39">
         <v>1.34375</v>
       </c>
-      <c r="AR1" s="42">
+      <c r="AR1" s="39">
         <v>1.3541666666666701</v>
       </c>
-      <c r="AS1" s="43">
+      <c r="AS1" s="40">
         <v>1.3645833333333399</v>
       </c>
-      <c r="AT1" s="41">
+      <c r="AT1" s="38">
         <v>1.375</v>
       </c>
-      <c r="AU1" s="42">
+      <c r="AU1" s="39">
         <v>1.3854166666666701</v>
       </c>
-      <c r="AV1" s="42">
+      <c r="AV1" s="39">
         <v>1.3958333333333399</v>
       </c>
-      <c r="AW1" s="43">
+      <c r="AW1" s="40">
         <v>1.40625</v>
       </c>
     </row>
     <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
+      <c r="A2" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -4311,13 +2271,13 @@
       <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="44" t="s">
+      <c r="B4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -4326,10 +2286,10 @@
       <c r="F4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="44" t="s">
+      <c r="G4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="14" t="s">
@@ -4338,10 +2298,10 @@
       <c r="J4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="44" t="s">
+      <c r="K4" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="M4" s="14" t="s">
@@ -4350,10 +2310,10 @@
       <c r="N4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="44" t="s">
+      <c r="O4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="Q4" s="14" t="s">
@@ -4362,10 +2322,10 @@
       <c r="R4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="T4" s="44" t="s">
+      <c r="S4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="U4" s="14" t="s">
@@ -4374,10 +2334,10 @@
       <c r="V4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="W4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="X4" s="44" t="s">
+      <c r="W4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Y4" s="14" t="s">
@@ -4386,10 +2346,10 @@
       <c r="Z4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AA4" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB4" s="44" t="s">
+      <c r="AA4" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="AC4" s="14" t="s">
@@ -4398,10 +2358,10 @@
       <c r="AD4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AE4" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF4" s="44" t="s">
+      <c r="AE4" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="AG4" s="14" t="s">
@@ -4410,10 +2370,10 @@
       <c r="AH4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AI4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="AJ4" s="44" t="s">
+      <c r="AI4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="AK4" s="14" t="s">
@@ -4422,10 +2382,10 @@
       <c r="AL4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AM4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="AN4" s="44" t="s">
+      <c r="AM4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="AO4" s="14" t="s">
@@ -4434,10 +2394,10 @@
       <c r="AP4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AQ4" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR4" s="44" t="s">
+      <c r="AQ4" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="AS4" s="14" t="s">
@@ -4446,10 +2406,10 @@
       <c r="AT4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AU4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="AV4" s="44" t="s">
+      <c r="AU4" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="AV4" s="41" t="s">
         <v>29</v>
       </c>
       <c r="AW4" s="14" t="s">
@@ -4460,13 +2420,13 @@
       <c r="A5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="41" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="14" t="s">
@@ -4475,10 +2435,10 @@
       <c r="F5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="44" t="s">
+      <c r="G5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="41" t="s">
         <v>2</v>
       </c>
       <c r="I5" s="14" t="s">
@@ -4487,10 +2447,10 @@
       <c r="J5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="44" t="s">
+      <c r="K5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="41" t="s">
         <v>30</v>
       </c>
       <c r="M5" s="14" t="s">
@@ -4499,10 +2459,10 @@
       <c r="N5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="O5" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="P5" s="44" t="s">
+      <c r="O5" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="P5" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q5" s="14" t="s">
@@ -4511,10 +2471,10 @@
       <c r="R5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="S5" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="T5" s="44" t="s">
+      <c r="S5" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="T5" s="41" t="s">
         <v>2</v>
       </c>
       <c r="U5" s="14" t="s">
@@ -4523,10 +2483,10 @@
       <c r="V5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="W5" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="X5" s="44" t="s">
+      <c r="W5" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="X5" s="41" t="s">
         <v>30</v>
       </c>
       <c r="Y5" s="14" t="s">
@@ -4535,10 +2495,10 @@
       <c r="Z5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB5" s="44" t="s">
+      <c r="AA5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB5" s="41" t="s">
         <v>30</v>
       </c>
       <c r="AC5" s="14" t="s">
@@ -4547,10 +2507,10 @@
       <c r="AD5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AE5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF5" s="44" t="s">
+      <c r="AE5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF5" s="41" t="s">
         <v>2</v>
       </c>
       <c r="AG5" s="14" t="s">
@@ -4559,10 +2519,10 @@
       <c r="AH5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AI5" s="44" t="s">
+      <c r="AI5" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="AJ5" s="44" t="s">
+      <c r="AJ5" s="41" t="s">
         <v>30</v>
       </c>
       <c r="AK5" s="14" t="s">
@@ -4571,10 +2531,10 @@
       <c r="AL5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AM5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AN5" s="44" t="s">
+      <c r="AM5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN5" s="41" t="s">
         <v>2</v>
       </c>
       <c r="AO5" s="14" t="s">
@@ -4583,10 +2543,10 @@
       <c r="AP5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AQ5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AR5" s="44" t="s">
+      <c r="AQ5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR5" s="41" t="s">
         <v>30</v>
       </c>
       <c r="AS5" s="14" t="s">
@@ -4595,10 +2555,10 @@
       <c r="AT5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AU5" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AV5" s="44" t="s">
+      <c r="AU5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AV5" s="41" t="s">
         <v>30</v>
       </c>
       <c r="AW5" s="14" t="s">
@@ -4609,13 +2569,13 @@
       <c r="A6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="14" t="s">
@@ -4624,10 +2584,10 @@
       <c r="F6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="44" t="s">
+      <c r="G6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="41" t="s">
         <v>2</v>
       </c>
       <c r="I6" s="14" t="s">
@@ -4636,10 +2596,10 @@
       <c r="J6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="44" t="s">
+      <c r="K6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="M6" s="14" t="s">
@@ -4648,10 +2608,10 @@
       <c r="N6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="O6" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="P6" s="44" t="s">
+      <c r="O6" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q6" s="14" t="s">
@@ -4660,10 +2620,10 @@
       <c r="R6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="T6" s="44" t="s">
+      <c r="S6" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="T6" s="41" t="s">
         <v>2</v>
       </c>
       <c r="U6" s="14" t="s">
@@ -4672,10 +2632,10 @@
       <c r="V6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="W6" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="X6" s="44" t="s">
+      <c r="W6" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="X6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="Y6" s="14" t="s">
@@ -4684,10 +2644,10 @@
       <c r="Z6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AA6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB6" s="44" t="s">
+      <c r="AA6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="AC6" s="14" t="s">
@@ -4696,10 +2656,10 @@
       <c r="AD6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AE6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF6" s="44" t="s">
+      <c r="AE6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF6" s="41" t="s">
         <v>2</v>
       </c>
       <c r="AG6" s="14" t="s">
@@ -4708,10 +2668,10 @@
       <c r="AH6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AI6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ6" s="44" t="s">
+      <c r="AI6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="AK6" s="14" t="s">
@@ -4720,10 +2680,10 @@
       <c r="AL6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AM6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AN6" s="44" t="s">
+      <c r="AM6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN6" s="41" t="s">
         <v>2</v>
       </c>
       <c r="AO6" s="14" t="s">
@@ -4732,10 +2692,10 @@
       <c r="AP6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AQ6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AR6" s="44" t="s">
+      <c r="AQ6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="AS6" s="14" t="s">
@@ -4744,10 +2704,10 @@
       <c r="AT6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AU6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AV6" s="44" t="s">
+      <c r="AU6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="AV6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="AW6" s="14" t="s">
@@ -4758,13 +2718,13 @@
       <c r="A7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="41" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="14" t="s">
@@ -4773,10 +2733,10 @@
       <c r="F7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="44" t="s">
+      <c r="G7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="41" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="14" t="s">
@@ -4785,10 +2745,10 @@
       <c r="J7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="44" t="s">
+      <c r="K7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="44" t="s">
+      <c r="L7" s="41" t="s">
         <v>32</v>
       </c>
       <c r="M7" s="14" t="s">
@@ -4797,10 +2757,10 @@
       <c r="N7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="O7" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="P7" s="44" t="s">
+      <c r="O7" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="P7" s="41" t="s">
         <v>2</v>
       </c>
       <c r="Q7" s="14" t="s">
@@ -4809,10 +2769,10 @@
       <c r="R7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="S7" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="T7" s="44" t="s">
+      <c r="S7" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="T7" s="41" t="s">
         <v>2</v>
       </c>
       <c r="U7" s="14" t="s">
@@ -4821,10 +2781,10 @@
       <c r="V7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="W7" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="X7" s="44" t="s">
+      <c r="W7" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="X7" s="41" t="s">
         <v>29</v>
       </c>
       <c r="Y7" s="14" t="s">
@@ -4833,10 +2793,10 @@
       <c r="Z7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AA7" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB7" s="44" t="s">
+      <c r="AA7" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB7" s="41" t="s">
         <v>29</v>
       </c>
       <c r="AC7" s="14" t="s">
@@ -4845,10 +2805,10 @@
       <c r="AD7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AE7" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF7" s="44" t="s">
+      <c r="AE7" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF7" s="41" t="s">
         <v>29</v>
       </c>
       <c r="AG7" s="14" t="s">
@@ -4857,10 +2817,10 @@
       <c r="AH7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI7" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ7" s="44" t="s">
+      <c r="AI7" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ7" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AK7" s="14" t="s">
@@ -4869,10 +2829,10 @@
       <c r="AL7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AM7" s="44" t="s">
+      <c r="AM7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="AN7" s="44" t="s">
+      <c r="AN7" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AO7" s="14" t="s">
@@ -4881,10 +2841,10 @@
       <c r="AP7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AQ7" s="44" t="s">
+      <c r="AQ7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="AR7" s="44" t="s">
+      <c r="AR7" s="41" t="s">
         <v>2</v>
       </c>
       <c r="AS7" s="14" t="s">
@@ -4893,10 +2853,10 @@
       <c r="AT7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AU7" s="44" t="s">
+      <c r="AU7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="AV7" s="44" t="s">
+      <c r="AV7" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AW7" s="14" t="s">
@@ -5053,7 +3013,7 @@
       </c>
     </row>
     <row r="9" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="30">
@@ -5250,7 +3210,7 @@
       </c>
     </row>
     <row r="10" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="30">
@@ -5447,7 +3407,7 @@
       </c>
     </row>
     <row r="11" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
@@ -5644,57 +3604,57 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="44"/>
     </row>
     <row r="13" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
@@ -5775,228 +3735,228 @@
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44" t="s">
+      <c r="G14" s="41"/>
+      <c r="H14" s="41" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44" t="s">
+      <c r="J14" s="41"/>
+      <c r="K14" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="L14" s="44" t="s">
+      <c r="L14" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="44" t="s">
+      <c r="M14" s="41" t="s">
         <v>33</v>
       </c>
       <c r="N14" s="13"/>
-      <c r="O14" s="44"/>
-      <c r="P14" s="44"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
       <c r="Q14" s="14"/>
-      <c r="R14" s="44"/>
-      <c r="S14" s="44"/>
-      <c r="T14" s="44"/>
-      <c r="U14" s="44"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="41"/>
+      <c r="U14" s="41"/>
       <c r="V14" s="13"/>
-      <c r="W14" s="44"/>
-      <c r="X14" s="44"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="41"/>
       <c r="Y14" s="14"/>
-      <c r="Z14" s="44"/>
-      <c r="AA14" s="44"/>
-      <c r="AB14" s="44"/>
-      <c r="AC14" s="44"/>
+      <c r="Z14" s="41"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="41"/>
+      <c r="AC14" s="41"/>
       <c r="AD14" s="13"/>
-      <c r="AE14" s="44"/>
-      <c r="AF14" s="44"/>
+      <c r="AE14" s="41"/>
+      <c r="AF14" s="41"/>
       <c r="AG14" s="14"/>
-      <c r="AH14" s="44"/>
-      <c r="AI14" s="44"/>
-      <c r="AJ14" s="44"/>
-      <c r="AK14" s="44"/>
+      <c r="AH14" s="41"/>
+      <c r="AI14" s="41"/>
+      <c r="AJ14" s="41"/>
+      <c r="AK14" s="41"/>
       <c r="AL14" s="13"/>
-      <c r="AM14" s="44"/>
-      <c r="AN14" s="44" t="s">
+      <c r="AM14" s="41"/>
+      <c r="AN14" s="41" t="s">
         <v>31</v>
       </c>
       <c r="AO14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="AP14" s="44" t="s">
+      <c r="AP14" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="AQ14" s="44" t="s">
+      <c r="AQ14" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="AR14" s="44" t="s">
+      <c r="AR14" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="AS14" s="44" t="s">
+      <c r="AS14" s="41" t="s">
         <v>32</v>
       </c>
       <c r="AT14" s="13"/>
-      <c r="AU14" s="44"/>
-      <c r="AV14" s="44"/>
+      <c r="AU14" s="41"/>
+      <c r="AV14" s="41"/>
       <c r="AW14" s="14"/>
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="14"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
       <c r="Q15" s="14"/>
-      <c r="R15" s="44"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="41"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="41"/>
       <c r="V15" s="13"/>
-      <c r="W15" s="44"/>
-      <c r="X15" s="44"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="41"/>
       <c r="Y15" s="14"/>
-      <c r="Z15" s="44"/>
-      <c r="AA15" s="44"/>
-      <c r="AB15" s="44"/>
-      <c r="AC15" s="44"/>
+      <c r="Z15" s="41"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="41"/>
+      <c r="AC15" s="41"/>
       <c r="AD15" s="13"/>
-      <c r="AE15" s="44"/>
-      <c r="AF15" s="44"/>
+      <c r="AE15" s="41"/>
+      <c r="AF15" s="41"/>
       <c r="AG15" s="14"/>
-      <c r="AH15" s="44"/>
-      <c r="AI15" s="44"/>
-      <c r="AJ15" s="44"/>
-      <c r="AK15" s="44"/>
+      <c r="AH15" s="41"/>
+      <c r="AI15" s="41"/>
+      <c r="AJ15" s="41"/>
+      <c r="AK15" s="41"/>
       <c r="AL15" s="13"/>
-      <c r="AM15" s="44"/>
-      <c r="AN15" s="44"/>
+      <c r="AM15" s="41"/>
+      <c r="AN15" s="41"/>
       <c r="AO15" s="14"/>
-      <c r="AP15" s="44"/>
-      <c r="AQ15" s="44"/>
-      <c r="AR15" s="44"/>
-      <c r="AS15" s="44"/>
+      <c r="AP15" s="41"/>
+      <c r="AQ15" s="41"/>
+      <c r="AR15" s="41"/>
+      <c r="AS15" s="41"/>
       <c r="AT15" s="13"/>
-      <c r="AU15" s="44"/>
-      <c r="AV15" s="44"/>
+      <c r="AU15" s="41"/>
+      <c r="AV15" s="41"/>
       <c r="AW15" s="14"/>
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
       <c r="F16" s="13"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
       <c r="N16" s="13"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="44"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
       <c r="Q16" s="14"/>
-      <c r="R16" s="44"/>
-      <c r="S16" s="44"/>
-      <c r="T16" s="44"/>
-      <c r="U16" s="44"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
       <c r="V16" s="13"/>
-      <c r="W16" s="44"/>
-      <c r="X16" s="44"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41"/>
       <c r="Y16" s="14"/>
-      <c r="Z16" s="44"/>
-      <c r="AA16" s="44"/>
-      <c r="AB16" s="44"/>
-      <c r="AC16" s="44"/>
+      <c r="Z16" s="41"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="41"/>
+      <c r="AC16" s="41"/>
       <c r="AD16" s="13"/>
-      <c r="AE16" s="44"/>
-      <c r="AF16" s="44"/>
+      <c r="AE16" s="41"/>
+      <c r="AF16" s="41"/>
       <c r="AG16" s="14"/>
-      <c r="AH16" s="44"/>
-      <c r="AI16" s="44"/>
-      <c r="AJ16" s="44"/>
-      <c r="AK16" s="44"/>
+      <c r="AH16" s="41"/>
+      <c r="AI16" s="41"/>
+      <c r="AJ16" s="41"/>
+      <c r="AK16" s="41"/>
       <c r="AL16" s="13"/>
-      <c r="AM16" s="44"/>
-      <c r="AN16" s="44"/>
+      <c r="AM16" s="41"/>
+      <c r="AN16" s="41"/>
       <c r="AO16" s="14"/>
-      <c r="AP16" s="44"/>
-      <c r="AQ16" s="44"/>
-      <c r="AR16" s="44"/>
-      <c r="AS16" s="44"/>
+      <c r="AP16" s="41"/>
+      <c r="AQ16" s="41"/>
+      <c r="AR16" s="41"/>
+      <c r="AS16" s="41"/>
       <c r="AT16" s="13"/>
-      <c r="AU16" s="44"/>
-      <c r="AV16" s="44"/>
+      <c r="AU16" s="41"/>
+      <c r="AV16" s="41"/>
       <c r="AW16" s="14"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
       <c r="N17" s="13"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="44"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
       <c r="Q17" s="14"/>
-      <c r="R17" s="44"/>
-      <c r="S17" s="44"/>
-      <c r="T17" s="44"/>
-      <c r="U17" s="44"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
       <c r="V17" s="13"/>
-      <c r="W17" s="44"/>
-      <c r="X17" s="44"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="41"/>
       <c r="Y17" s="14"/>
-      <c r="Z17" s="44"/>
-      <c r="AA17" s="44"/>
-      <c r="AB17" s="44"/>
-      <c r="AC17" s="44"/>
+      <c r="Z17" s="41"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="41"/>
+      <c r="AC17" s="41"/>
       <c r="AD17" s="13"/>
-      <c r="AE17" s="44"/>
-      <c r="AF17" s="44"/>
+      <c r="AE17" s="41"/>
+      <c r="AF17" s="41"/>
       <c r="AG17" s="14"/>
-      <c r="AH17" s="44"/>
-      <c r="AI17" s="44"/>
-      <c r="AJ17" s="44"/>
-      <c r="AK17" s="44"/>
+      <c r="AH17" s="41"/>
+      <c r="AI17" s="41"/>
+      <c r="AJ17" s="41"/>
+      <c r="AK17" s="41"/>
       <c r="AL17" s="13"/>
-      <c r="AM17" s="44"/>
-      <c r="AN17" s="44"/>
+      <c r="AM17" s="41"/>
+      <c r="AN17" s="41"/>
       <c r="AO17" s="14"/>
-      <c r="AP17" s="44"/>
-      <c r="AQ17" s="44"/>
-      <c r="AR17" s="44"/>
-      <c r="AS17" s="44"/>
+      <c r="AP17" s="41"/>
+      <c r="AQ17" s="41"/>
+      <c r="AR17" s="41"/>
+      <c r="AS17" s="41"/>
       <c r="AT17" s="13"/>
-      <c r="AU17" s="44"/>
-      <c r="AV17" s="44"/>
+      <c r="AU17" s="41"/>
+      <c r="AV17" s="41"/>
       <c r="AW17" s="14"/>
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6051,7 +4011,7 @@
       <c r="AW18" s="17"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="30">
@@ -6248,7 +4208,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="30">
@@ -6445,7 +4405,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="28" t="str">
@@ -6642,7 +4602,7 @@
       </c>
     </row>
     <row r="22" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="37" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="33" t="str">
@@ -6844,42 +4804,42 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW8 B13:AW18">
-    <cfRule type="cellIs" dxfId="163" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="162" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="5" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="6" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="8" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="9" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="11" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="12" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="14" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="15" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="16" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6916,203 +4876,203 @@
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41">
+      <c r="B1" s="38">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C1" s="42">
+      <c r="C1" s="39">
         <v>0.92708333333333337</v>
       </c>
-      <c r="D1" s="42">
+      <c r="D1" s="39">
         <v>0.9375</v>
       </c>
-      <c r="E1" s="43">
+      <c r="E1" s="40">
         <v>0.94791666666666663</v>
       </c>
-      <c r="F1" s="41">
+      <c r="F1" s="38">
         <v>0.95833333333333404</v>
       </c>
-      <c r="G1" s="42">
+      <c r="G1" s="39">
         <v>0.96875</v>
       </c>
-      <c r="H1" s="42">
+      <c r="H1" s="39">
         <v>0.97916666666666696</v>
       </c>
-      <c r="I1" s="43">
+      <c r="I1" s="40">
         <v>0.98958333333333404</v>
       </c>
-      <c r="J1" s="41">
+      <c r="J1" s="38">
         <v>1</v>
       </c>
-      <c r="K1" s="42">
+      <c r="K1" s="39">
         <v>1.0104166666666701</v>
       </c>
-      <c r="L1" s="42">
+      <c r="L1" s="39">
         <v>1.0208333333333299</v>
       </c>
-      <c r="M1" s="43">
+      <c r="M1" s="40">
         <v>1.03125</v>
       </c>
-      <c r="N1" s="41">
+      <c r="N1" s="38">
         <v>1.0416666666666701</v>
       </c>
-      <c r="O1" s="42">
+      <c r="O1" s="39">
         <v>1.0520833333333299</v>
       </c>
-      <c r="P1" s="42">
+      <c r="P1" s="39">
         <v>1.0625</v>
       </c>
-      <c r="Q1" s="43">
+      <c r="Q1" s="40">
         <v>1.0729166666666701</v>
       </c>
-      <c r="R1" s="41">
+      <c r="R1" s="38">
         <v>1.0833333333333299</v>
       </c>
-      <c r="S1" s="42">
+      <c r="S1" s="39">
         <v>1.09375</v>
       </c>
-      <c r="T1" s="42">
+      <c r="T1" s="39">
         <v>1.1041666666666701</v>
       </c>
-      <c r="U1" s="43">
+      <c r="U1" s="40">
         <v>1.1145833333333299</v>
       </c>
-      <c r="V1" s="41">
+      <c r="V1" s="38">
         <v>1.125</v>
       </c>
-      <c r="W1" s="42">
+      <c r="W1" s="39">
         <v>1.1354166666666701</v>
       </c>
-      <c r="X1" s="42">
+      <c r="X1" s="39">
         <v>1.1458333333333299</v>
       </c>
-      <c r="Y1" s="43">
+      <c r="Y1" s="40">
         <v>1.15625</v>
       </c>
-      <c r="Z1" s="41">
+      <c r="Z1" s="38">
         <v>1.1666666666666701</v>
       </c>
-      <c r="AA1" s="42">
+      <c r="AA1" s="39">
         <v>1.1770833333333399</v>
       </c>
-      <c r="AB1" s="42">
+      <c r="AB1" s="39">
         <v>1.1875</v>
       </c>
-      <c r="AC1" s="43">
+      <c r="AC1" s="40">
         <v>1.1979166666666701</v>
       </c>
-      <c r="AD1" s="41">
+      <c r="AD1" s="38">
         <v>1.2083333333333399</v>
       </c>
-      <c r="AE1" s="42">
+      <c r="AE1" s="39">
         <v>1.21875</v>
       </c>
-      <c r="AF1" s="42">
+      <c r="AF1" s="39">
         <v>1.2291666666666701</v>
       </c>
-      <c r="AG1" s="43">
+      <c r="AG1" s="40">
         <v>1.2395833333333399</v>
       </c>
-      <c r="AH1" s="41">
+      <c r="AH1" s="38">
         <v>1.25</v>
       </c>
-      <c r="AI1" s="42">
+      <c r="AI1" s="39">
         <v>1.2604166666666701</v>
       </c>
-      <c r="AJ1" s="42">
+      <c r="AJ1" s="39">
         <v>1.2708333333333399</v>
       </c>
-      <c r="AK1" s="43">
+      <c r="AK1" s="40">
         <v>1.28125</v>
       </c>
-      <c r="AL1" s="41">
+      <c r="AL1" s="38">
         <v>1.2916666666666701</v>
       </c>
-      <c r="AM1" s="42">
+      <c r="AM1" s="39">
         <v>1.3020833333333399</v>
       </c>
-      <c r="AN1" s="42">
+      <c r="AN1" s="39">
         <v>1.3125</v>
       </c>
-      <c r="AO1" s="43">
+      <c r="AO1" s="40">
         <v>1.3229166666666701</v>
       </c>
-      <c r="AP1" s="41">
+      <c r="AP1" s="38">
         <v>1.3333333333333399</v>
       </c>
-      <c r="AQ1" s="42">
+      <c r="AQ1" s="39">
         <v>1.34375</v>
       </c>
-      <c r="AR1" s="42">
+      <c r="AR1" s="39">
         <v>1.3541666666666701</v>
       </c>
-      <c r="AS1" s="43">
+      <c r="AS1" s="40">
         <v>1.3645833333333399</v>
       </c>
-      <c r="AT1" s="41">
+      <c r="AT1" s="38">
         <v>1.375</v>
       </c>
-      <c r="AU1" s="42">
+      <c r="AU1" s="39">
         <v>1.3854166666666701</v>
       </c>
-      <c r="AV1" s="42">
+      <c r="AV1" s="39">
         <v>1.3958333333333399</v>
       </c>
-      <c r="AW1" s="43">
+      <c r="AW1" s="40">
         <v>1.40625</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
+      <c r="A2" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -8033,7 +5993,7 @@
       </c>
     </row>
     <row r="9" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="30">
@@ -8230,7 +6190,7 @@
       </c>
     </row>
     <row r="10" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="30">
@@ -8427,7 +6387,7 @@
       </c>
     </row>
     <row r="11" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
@@ -8624,57 +6584,57 @@
       </c>
     </row>
     <row r="12" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="44"/>
     </row>
     <row r="13" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -9031,7 +6991,7 @@
       <c r="AW18" s="27"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="30">
@@ -9228,7 +7188,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="30">
@@ -9425,7 +7385,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="28" t="str">
@@ -9622,7 +7582,7 @@
       </c>
     </row>
     <row r="22" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="37" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="33" t="str">
@@ -9824,40 +7784,40 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="151" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="67" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="68" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="69" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="70" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="71" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="72" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="73" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="74" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="75" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="76" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="77" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="78" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10040,57 +8000,57 @@
       </c>
     </row>
     <row r="2" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
+      <c r="A2" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -11011,7 +8971,7 @@
       </c>
     </row>
     <row r="9" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="30">
@@ -11208,7 +9168,7 @@
       </c>
     </row>
     <row r="10" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="30">
@@ -11405,7 +9365,7 @@
       </c>
     </row>
     <row r="11" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
@@ -11602,57 +9562,57 @@
       </c>
     </row>
     <row r="12" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="44"/>
     </row>
     <row r="13" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -12009,7 +9969,7 @@
       <c r="AW18" s="27"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="30">
@@ -12206,7 +10166,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="30">
@@ -12403,7 +10363,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="28" t="str">
@@ -12600,7 +10560,7 @@
       </c>
     </row>
     <row r="22" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="37" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="33" t="str">
@@ -12802,40 +10762,40 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="139" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="134" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="12" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12872,203 +10832,203 @@
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41">
+      <c r="B1" s="38">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C1" s="42">
+      <c r="C1" s="39">
         <v>0.92708333333333337</v>
       </c>
-      <c r="D1" s="42">
+      <c r="D1" s="39">
         <v>0.9375</v>
       </c>
-      <c r="E1" s="43">
+      <c r="E1" s="40">
         <v>0.94791666666666663</v>
       </c>
-      <c r="F1" s="41">
+      <c r="F1" s="38">
         <v>0.95833333333333404</v>
       </c>
-      <c r="G1" s="42">
+      <c r="G1" s="39">
         <v>0.96875</v>
       </c>
-      <c r="H1" s="42">
+      <c r="H1" s="39">
         <v>0.97916666666666696</v>
       </c>
-      <c r="I1" s="43">
+      <c r="I1" s="40">
         <v>0.98958333333333404</v>
       </c>
-      <c r="J1" s="41">
+      <c r="J1" s="38">
         <v>1</v>
       </c>
-      <c r="K1" s="42">
+      <c r="K1" s="39">
         <v>1.0104166666666701</v>
       </c>
-      <c r="L1" s="42">
+      <c r="L1" s="39">
         <v>1.0208333333333299</v>
       </c>
-      <c r="M1" s="43">
+      <c r="M1" s="40">
         <v>1.03125</v>
       </c>
-      <c r="N1" s="41">
+      <c r="N1" s="38">
         <v>1.0416666666666701</v>
       </c>
-      <c r="O1" s="42">
+      <c r="O1" s="39">
         <v>1.0520833333333299</v>
       </c>
-      <c r="P1" s="42">
+      <c r="P1" s="39">
         <v>1.0625</v>
       </c>
-      <c r="Q1" s="43">
+      <c r="Q1" s="40">
         <v>1.0729166666666701</v>
       </c>
-      <c r="R1" s="41">
+      <c r="R1" s="38">
         <v>1.0833333333333299</v>
       </c>
-      <c r="S1" s="42">
+      <c r="S1" s="39">
         <v>1.09375</v>
       </c>
-      <c r="T1" s="42">
+      <c r="T1" s="39">
         <v>1.1041666666666701</v>
       </c>
-      <c r="U1" s="43">
+      <c r="U1" s="40">
         <v>1.1145833333333299</v>
       </c>
-      <c r="V1" s="41">
+      <c r="V1" s="38">
         <v>1.125</v>
       </c>
-      <c r="W1" s="42">
+      <c r="W1" s="39">
         <v>1.1354166666666701</v>
       </c>
-      <c r="X1" s="42">
+      <c r="X1" s="39">
         <v>1.1458333333333299</v>
       </c>
-      <c r="Y1" s="43">
+      <c r="Y1" s="40">
         <v>1.15625</v>
       </c>
-      <c r="Z1" s="41">
+      <c r="Z1" s="38">
         <v>1.1666666666666701</v>
       </c>
-      <c r="AA1" s="42">
+      <c r="AA1" s="39">
         <v>1.1770833333333399</v>
       </c>
-      <c r="AB1" s="42">
+      <c r="AB1" s="39">
         <v>1.1875</v>
       </c>
-      <c r="AC1" s="43">
+      <c r="AC1" s="40">
         <v>1.1979166666666701</v>
       </c>
-      <c r="AD1" s="41">
+      <c r="AD1" s="38">
         <v>1.2083333333333399</v>
       </c>
-      <c r="AE1" s="42">
+      <c r="AE1" s="39">
         <v>1.21875</v>
       </c>
-      <c r="AF1" s="42">
+      <c r="AF1" s="39">
         <v>1.2291666666666701</v>
       </c>
-      <c r="AG1" s="43">
+      <c r="AG1" s="40">
         <v>1.2395833333333399</v>
       </c>
-      <c r="AH1" s="41">
+      <c r="AH1" s="38">
         <v>1.25</v>
       </c>
-      <c r="AI1" s="42">
+      <c r="AI1" s="39">
         <v>1.2604166666666701</v>
       </c>
-      <c r="AJ1" s="42">
+      <c r="AJ1" s="39">
         <v>1.2708333333333399</v>
       </c>
-      <c r="AK1" s="43">
+      <c r="AK1" s="40">
         <v>1.28125</v>
       </c>
-      <c r="AL1" s="41">
+      <c r="AL1" s="38">
         <v>1.2916666666666701</v>
       </c>
-      <c r="AM1" s="42">
+      <c r="AM1" s="39">
         <v>1.3020833333333399</v>
       </c>
-      <c r="AN1" s="42">
+      <c r="AN1" s="39">
         <v>1.3125</v>
       </c>
-      <c r="AO1" s="43">
+      <c r="AO1" s="40">
         <v>1.3229166666666701</v>
       </c>
-      <c r="AP1" s="41">
+      <c r="AP1" s="38">
         <v>1.3333333333333399</v>
       </c>
-      <c r="AQ1" s="42">
+      <c r="AQ1" s="39">
         <v>1.34375</v>
       </c>
-      <c r="AR1" s="42">
+      <c r="AR1" s="39">
         <v>1.3541666666666701</v>
       </c>
-      <c r="AS1" s="43">
+      <c r="AS1" s="40">
         <v>1.3645833333333399</v>
       </c>
-      <c r="AT1" s="41">
+      <c r="AT1" s="38">
         <v>1.375</v>
       </c>
-      <c r="AU1" s="42">
+      <c r="AU1" s="39">
         <v>1.3854166666666701</v>
       </c>
-      <c r="AV1" s="42">
+      <c r="AV1" s="39">
         <v>1.3958333333333399</v>
       </c>
-      <c r="AW1" s="43">
+      <c r="AW1" s="40">
         <v>1.40625</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
+      <c r="A2" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -13989,7 +11949,7 @@
       </c>
     </row>
     <row r="9" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="30">
@@ -14186,7 +12146,7 @@
       </c>
     </row>
     <row r="10" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="30">
@@ -14383,7 +12343,7 @@
       </c>
     </row>
     <row r="11" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
@@ -14580,57 +12540,57 @@
       </c>
     </row>
     <row r="12" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="44"/>
     </row>
     <row r="13" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -14987,7 +12947,7 @@
       <c r="AW18" s="27"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="30">
@@ -15184,7 +13144,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="30">
@@ -15381,7 +13341,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="28" t="str">
@@ -15780,91 +13740,91 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="127" priority="62">
+    <cfRule type="expression" dxfId="75" priority="62">
       <formula>#REF!&gt;=$B$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:AW18">
-    <cfRule type="cellIs" dxfId="126" priority="38" operator="equal">
-      <formula>"Dcar1"</formula>
+  <conditionalFormatting sqref="B3:AW10 B13:AW20">
+    <cfRule type="cellIs" dxfId="74" priority="1" operator="equal">
+      <formula>"AL1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="equal">
+      <formula>"Acar1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="3" operator="equal">
+      <formula>"AL2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="4" operator="equal">
+      <formula>"Acar2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="5" operator="equal">
+      <formula>"AL3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="6" operator="equal">
+      <formula>"Acar3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="7" operator="equal">
+      <formula>"AL4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="8" operator="equal">
+      <formula>"Acar4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="9" operator="equal">
+      <formula>"AL5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="10" operator="equal">
+      <formula>"Acar5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="11" operator="equal">
+      <formula>"AL6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="12" operator="equal">
+      <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="125" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="37" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="39" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="40" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="41" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="42" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="43" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="44" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="45" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="46" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="47" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="48" operator="equal">
       <formula>"Dcar6"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:AW10 B19:AW20">
-    <cfRule type="cellIs" dxfId="114" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="50" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="113" priority="1" operator="equal">
-      <formula>"AL1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="2" operator="equal">
-      <formula>"Acar1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="3" operator="equal">
-      <formula>"AL2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="4" operator="equal">
-      <formula>"Acar2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="5" operator="equal">
-      <formula>"AL3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="6" operator="equal">
-      <formula>"Acar3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="7" operator="equal">
-      <formula>"AL4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="8" operator="equal">
-      <formula>"Acar4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="9" operator="equal">
-      <formula>"AL5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="10" operator="equal">
-      <formula>"Acar5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="11" operator="equal">
-      <formula>"AL6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="12" operator="equal">
-      <formula>"Acar6"</formula>
+  <conditionalFormatting sqref="B13:AW18">
+    <cfRule type="cellIs" dxfId="50" priority="38" operator="equal">
+      <formula>"Dcar1"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15900,203 +13860,203 @@
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41">
+      <c r="B1" s="38">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C1" s="42">
+      <c r="C1" s="39">
         <v>0.92708333333333337</v>
       </c>
-      <c r="D1" s="42">
+      <c r="D1" s="39">
         <v>0.9375</v>
       </c>
-      <c r="E1" s="43">
+      <c r="E1" s="40">
         <v>0.94791666666666663</v>
       </c>
-      <c r="F1" s="41">
+      <c r="F1" s="38">
         <v>0.95833333333333404</v>
       </c>
-      <c r="G1" s="42">
+      <c r="G1" s="39">
         <v>0.96875</v>
       </c>
-      <c r="H1" s="42">
+      <c r="H1" s="39">
         <v>0.97916666666666696</v>
       </c>
-      <c r="I1" s="43">
+      <c r="I1" s="40">
         <v>0.98958333333333404</v>
       </c>
-      <c r="J1" s="41">
+      <c r="J1" s="38">
         <v>1</v>
       </c>
-      <c r="K1" s="42">
+      <c r="K1" s="39">
         <v>1.0104166666666701</v>
       </c>
-      <c r="L1" s="42">
+      <c r="L1" s="39">
         <v>1.0208333333333299</v>
       </c>
-      <c r="M1" s="43">
+      <c r="M1" s="40">
         <v>1.03125</v>
       </c>
-      <c r="N1" s="41">
+      <c r="N1" s="38">
         <v>1.0416666666666701</v>
       </c>
-      <c r="O1" s="42">
+      <c r="O1" s="39">
         <v>1.0520833333333299</v>
       </c>
-      <c r="P1" s="42">
+      <c r="P1" s="39">
         <v>1.0625</v>
       </c>
-      <c r="Q1" s="43">
+      <c r="Q1" s="40">
         <v>1.0729166666666701</v>
       </c>
-      <c r="R1" s="41">
+      <c r="R1" s="38">
         <v>1.0833333333333299</v>
       </c>
-      <c r="S1" s="42">
+      <c r="S1" s="39">
         <v>1.09375</v>
       </c>
-      <c r="T1" s="42">
+      <c r="T1" s="39">
         <v>1.1041666666666701</v>
       </c>
-      <c r="U1" s="43">
+      <c r="U1" s="40">
         <v>1.1145833333333299</v>
       </c>
-      <c r="V1" s="41">
+      <c r="V1" s="38">
         <v>1.125</v>
       </c>
-      <c r="W1" s="42">
+      <c r="W1" s="39">
         <v>1.1354166666666701</v>
       </c>
-      <c r="X1" s="42">
+      <c r="X1" s="39">
         <v>1.1458333333333299</v>
       </c>
-      <c r="Y1" s="43">
+      <c r="Y1" s="40">
         <v>1.15625</v>
       </c>
-      <c r="Z1" s="41">
+      <c r="Z1" s="38">
         <v>1.1666666666666701</v>
       </c>
-      <c r="AA1" s="42">
+      <c r="AA1" s="39">
         <v>1.1770833333333399</v>
       </c>
-      <c r="AB1" s="42">
+      <c r="AB1" s="39">
         <v>1.1875</v>
       </c>
-      <c r="AC1" s="43">
+      <c r="AC1" s="40">
         <v>1.1979166666666701</v>
       </c>
-      <c r="AD1" s="41">
+      <c r="AD1" s="38">
         <v>1.2083333333333399</v>
       </c>
-      <c r="AE1" s="42">
+      <c r="AE1" s="39">
         <v>1.21875</v>
       </c>
-      <c r="AF1" s="42">
+      <c r="AF1" s="39">
         <v>1.2291666666666701</v>
       </c>
-      <c r="AG1" s="43">
+      <c r="AG1" s="40">
         <v>1.2395833333333399</v>
       </c>
-      <c r="AH1" s="41">
+      <c r="AH1" s="38">
         <v>1.25</v>
       </c>
-      <c r="AI1" s="42">
+      <c r="AI1" s="39">
         <v>1.2604166666666701</v>
       </c>
-      <c r="AJ1" s="42">
+      <c r="AJ1" s="39">
         <v>1.2708333333333399</v>
       </c>
-      <c r="AK1" s="43">
+      <c r="AK1" s="40">
         <v>1.28125</v>
       </c>
-      <c r="AL1" s="41">
+      <c r="AL1" s="38">
         <v>1.2916666666666701</v>
       </c>
-      <c r="AM1" s="42">
+      <c r="AM1" s="39">
         <v>1.3020833333333399</v>
       </c>
-      <c r="AN1" s="42">
+      <c r="AN1" s="39">
         <v>1.3125</v>
       </c>
-      <c r="AO1" s="43">
+      <c r="AO1" s="40">
         <v>1.3229166666666701</v>
       </c>
-      <c r="AP1" s="41">
+      <c r="AP1" s="38">
         <v>1.3333333333333399</v>
       </c>
-      <c r="AQ1" s="42">
+      <c r="AQ1" s="39">
         <v>1.34375</v>
       </c>
-      <c r="AR1" s="42">
+      <c r="AR1" s="39">
         <v>1.3541666666666701</v>
       </c>
-      <c r="AS1" s="43">
+      <c r="AS1" s="40">
         <v>1.3645833333333399</v>
       </c>
-      <c r="AT1" s="41">
+      <c r="AT1" s="38">
         <v>1.375</v>
       </c>
-      <c r="AU1" s="42">
+      <c r="AU1" s="39">
         <v>1.3854166666666701</v>
       </c>
-      <c r="AV1" s="42">
+      <c r="AV1" s="39">
         <v>1.3958333333333399</v>
       </c>
-      <c r="AW1" s="43">
+      <c r="AW1" s="40">
         <v>1.40625</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
+      <c r="A2" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -17017,7 +14977,7 @@
       </c>
     </row>
     <row r="9" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="30">
@@ -17214,7 +15174,7 @@
       </c>
     </row>
     <row r="10" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="30">
@@ -17411,7 +15371,7 @@
       </c>
     </row>
     <row r="11" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
@@ -17608,57 +15568,57 @@
       </c>
     </row>
     <row r="12" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="44"/>
     </row>
     <row r="13" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -18007,7 +15967,7 @@
       <c r="AW18" s="27"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="30">
@@ -18204,7 +16164,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="30">
@@ -18401,7 +16361,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="28" t="str">
@@ -18800,40 +16760,40 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="101" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="6" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="7" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="8" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="9" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="10" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="11" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="12" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="13" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="14" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="15" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="16" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="17" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18870,203 +16830,203 @@
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41">
+      <c r="B1" s="38">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C1" s="42">
+      <c r="C1" s="39">
         <v>0.92708333333333337</v>
       </c>
-      <c r="D1" s="42">
+      <c r="D1" s="39">
         <v>0.9375</v>
       </c>
-      <c r="E1" s="43">
+      <c r="E1" s="40">
         <v>0.94791666666666663</v>
       </c>
-      <c r="F1" s="41">
+      <c r="F1" s="38">
         <v>0.95833333333333404</v>
       </c>
-      <c r="G1" s="42">
+      <c r="G1" s="39">
         <v>0.96875</v>
       </c>
-      <c r="H1" s="42">
+      <c r="H1" s="39">
         <v>0.97916666666666696</v>
       </c>
-      <c r="I1" s="43">
+      <c r="I1" s="40">
         <v>0.98958333333333404</v>
       </c>
-      <c r="J1" s="41">
+      <c r="J1" s="38">
         <v>1</v>
       </c>
-      <c r="K1" s="42">
+      <c r="K1" s="39">
         <v>1.0104166666666701</v>
       </c>
-      <c r="L1" s="42">
+      <c r="L1" s="39">
         <v>1.0208333333333299</v>
       </c>
-      <c r="M1" s="43">
+      <c r="M1" s="40">
         <v>1.03125</v>
       </c>
-      <c r="N1" s="41">
+      <c r="N1" s="38">
         <v>1.0416666666666701</v>
       </c>
-      <c r="O1" s="42">
+      <c r="O1" s="39">
         <v>1.0520833333333299</v>
       </c>
-      <c r="P1" s="42">
+      <c r="P1" s="39">
         <v>1.0625</v>
       </c>
-      <c r="Q1" s="43">
+      <c r="Q1" s="40">
         <v>1.0729166666666701</v>
       </c>
-      <c r="R1" s="41">
+      <c r="R1" s="38">
         <v>1.0833333333333299</v>
       </c>
-      <c r="S1" s="42">
+      <c r="S1" s="39">
         <v>1.09375</v>
       </c>
-      <c r="T1" s="42">
+      <c r="T1" s="39">
         <v>1.1041666666666701</v>
       </c>
-      <c r="U1" s="43">
+      <c r="U1" s="40">
         <v>1.1145833333333299</v>
       </c>
-      <c r="V1" s="41">
+      <c r="V1" s="38">
         <v>1.125</v>
       </c>
-      <c r="W1" s="42">
+      <c r="W1" s="39">
         <v>1.1354166666666701</v>
       </c>
-      <c r="X1" s="42">
+      <c r="X1" s="39">
         <v>1.1458333333333299</v>
       </c>
-      <c r="Y1" s="43">
+      <c r="Y1" s="40">
         <v>1.15625</v>
       </c>
-      <c r="Z1" s="41">
+      <c r="Z1" s="38">
         <v>1.1666666666666701</v>
       </c>
-      <c r="AA1" s="42">
+      <c r="AA1" s="39">
         <v>1.1770833333333399</v>
       </c>
-      <c r="AB1" s="42">
+      <c r="AB1" s="39">
         <v>1.1875</v>
       </c>
-      <c r="AC1" s="43">
+      <c r="AC1" s="40">
         <v>1.1979166666666701</v>
       </c>
-      <c r="AD1" s="41">
+      <c r="AD1" s="38">
         <v>1.2083333333333399</v>
       </c>
-      <c r="AE1" s="42">
+      <c r="AE1" s="39">
         <v>1.21875</v>
       </c>
-      <c r="AF1" s="42">
+      <c r="AF1" s="39">
         <v>1.2291666666666701</v>
       </c>
-      <c r="AG1" s="43">
+      <c r="AG1" s="40">
         <v>1.2395833333333399</v>
       </c>
-      <c r="AH1" s="41">
+      <c r="AH1" s="38">
         <v>1.25</v>
       </c>
-      <c r="AI1" s="42">
+      <c r="AI1" s="39">
         <v>1.2604166666666701</v>
       </c>
-      <c r="AJ1" s="42">
+      <c r="AJ1" s="39">
         <v>1.2708333333333399</v>
       </c>
-      <c r="AK1" s="43">
+      <c r="AK1" s="40">
         <v>1.28125</v>
       </c>
-      <c r="AL1" s="41">
+      <c r="AL1" s="38">
         <v>1.2916666666666701</v>
       </c>
-      <c r="AM1" s="42">
+      <c r="AM1" s="39">
         <v>1.3020833333333399</v>
       </c>
-      <c r="AN1" s="42">
+      <c r="AN1" s="39">
         <v>1.3125</v>
       </c>
-      <c r="AO1" s="43">
+      <c r="AO1" s="40">
         <v>1.3229166666666701</v>
       </c>
-      <c r="AP1" s="41">
+      <c r="AP1" s="38">
         <v>1.3333333333333399</v>
       </c>
-      <c r="AQ1" s="42">
+      <c r="AQ1" s="39">
         <v>1.34375</v>
       </c>
-      <c r="AR1" s="42">
+      <c r="AR1" s="39">
         <v>1.3541666666666701</v>
       </c>
-      <c r="AS1" s="43">
+      <c r="AS1" s="40">
         <v>1.3645833333333399</v>
       </c>
-      <c r="AT1" s="41">
+      <c r="AT1" s="38">
         <v>1.375</v>
       </c>
-      <c r="AU1" s="42">
+      <c r="AU1" s="39">
         <v>1.3854166666666701</v>
       </c>
-      <c r="AV1" s="42">
+      <c r="AV1" s="39">
         <v>1.3958333333333399</v>
       </c>
-      <c r="AW1" s="43">
+      <c r="AW1" s="40">
         <v>1.40625</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
+      <c r="A2" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -19987,7 +17947,7 @@
       </c>
     </row>
     <row r="9" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="30">
@@ -20184,7 +18144,7 @@
       </c>
     </row>
     <row r="10" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="30">
@@ -20381,7 +18341,7 @@
       </c>
     </row>
     <row r="11" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
@@ -20578,57 +18538,57 @@
       </c>
     </row>
     <row r="12" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="44"/>
     </row>
     <row r="13" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -20977,7 +18937,7 @@
       <c r="AW18" s="27"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="30">
@@ -21174,7 +19134,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="30">
@@ -21371,7 +19331,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="28" t="str">
@@ -21770,91 +19730,91 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="89" priority="38">
+    <cfRule type="expression" dxfId="37" priority="38">
       <formula>#REF!&gt;=$B$1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:AW18">
-    <cfRule type="cellIs" dxfId="88" priority="14" operator="equal">
-      <formula>"Dcar1"</formula>
+  <conditionalFormatting sqref="B3:AW10 B13:AW20">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+      <formula>"AL1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+      <formula>"Acar1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
+      <formula>"AL2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
+      <formula>"Acar2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="5" operator="equal">
+      <formula>"AL3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="6" operator="equal">
+      <formula>"Acar3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
+      <formula>"AL4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
+      <formula>"Acar4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="9" operator="equal">
+      <formula>"AL5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
+      <formula>"Acar5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="11" operator="equal">
+      <formula>"AL6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="12" operator="equal">
+      <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="87" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="13" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="15" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="16" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="17" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="18" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="21" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="22" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="23" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="24" operator="equal">
       <formula>"Dcar6"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:AW10 B19:AW20">
-    <cfRule type="cellIs" dxfId="76" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="26" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="75" priority="1" operator="equal">
-      <formula>"AL1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="2" operator="equal">
-      <formula>"Acar1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="3" operator="equal">
-      <formula>"AL2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="4" operator="equal">
-      <formula>"Acar2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="5" operator="equal">
-      <formula>"AL3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="6" operator="equal">
-      <formula>"Acar3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="equal">
-      <formula>"AL4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="equal">
-      <formula>"Acar4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="9" operator="equal">
-      <formula>"AL5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="10" operator="equal">
-      <formula>"Acar5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="11" operator="equal">
-      <formula>"AL6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
-      <formula>"Acar6"</formula>
+  <conditionalFormatting sqref="B13:AW18">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
+      <formula>"Dcar1"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21890,203 +19850,203 @@
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41">
+      <c r="B1" s="38">
         <v>0.91666666666666663</v>
       </c>
-      <c r="C1" s="42">
+      <c r="C1" s="39">
         <v>0.92708333333333337</v>
       </c>
-      <c r="D1" s="42">
+      <c r="D1" s="39">
         <v>0.9375</v>
       </c>
-      <c r="E1" s="43">
+      <c r="E1" s="40">
         <v>0.94791666666666663</v>
       </c>
-      <c r="F1" s="41">
+      <c r="F1" s="38">
         <v>0.95833333333333404</v>
       </c>
-      <c r="G1" s="42">
+      <c r="G1" s="39">
         <v>0.96875</v>
       </c>
-      <c r="H1" s="42">
+      <c r="H1" s="39">
         <v>0.97916666666666696</v>
       </c>
-      <c r="I1" s="43">
+      <c r="I1" s="40">
         <v>0.98958333333333404</v>
       </c>
-      <c r="J1" s="41">
+      <c r="J1" s="38">
         <v>1</v>
       </c>
-      <c r="K1" s="42">
+      <c r="K1" s="39">
         <v>1.0104166666666701</v>
       </c>
-      <c r="L1" s="42">
+      <c r="L1" s="39">
         <v>1.0208333333333299</v>
       </c>
-      <c r="M1" s="43">
+      <c r="M1" s="40">
         <v>1.03125</v>
       </c>
-      <c r="N1" s="41">
+      <c r="N1" s="38">
         <v>1.0416666666666701</v>
       </c>
-      <c r="O1" s="42">
+      <c r="O1" s="39">
         <v>1.0520833333333299</v>
       </c>
-      <c r="P1" s="42">
+      <c r="P1" s="39">
         <v>1.0625</v>
       </c>
-      <c r="Q1" s="43">
+      <c r="Q1" s="40">
         <v>1.0729166666666701</v>
       </c>
-      <c r="R1" s="41">
+      <c r="R1" s="38">
         <v>1.0833333333333299</v>
       </c>
-      <c r="S1" s="42">
+      <c r="S1" s="39">
         <v>1.09375</v>
       </c>
-      <c r="T1" s="42">
+      <c r="T1" s="39">
         <v>1.1041666666666701</v>
       </c>
-      <c r="U1" s="43">
+      <c r="U1" s="40">
         <v>1.1145833333333299</v>
       </c>
-      <c r="V1" s="41">
+      <c r="V1" s="38">
         <v>1.125</v>
       </c>
-      <c r="W1" s="42">
+      <c r="W1" s="39">
         <v>1.1354166666666701</v>
       </c>
-      <c r="X1" s="42">
+      <c r="X1" s="39">
         <v>1.1458333333333299</v>
       </c>
-      <c r="Y1" s="43">
+      <c r="Y1" s="40">
         <v>1.15625</v>
       </c>
-      <c r="Z1" s="41">
+      <c r="Z1" s="38">
         <v>1.1666666666666701</v>
       </c>
-      <c r="AA1" s="42">
+      <c r="AA1" s="39">
         <v>1.1770833333333399</v>
       </c>
-      <c r="AB1" s="42">
+      <c r="AB1" s="39">
         <v>1.1875</v>
       </c>
-      <c r="AC1" s="43">
+      <c r="AC1" s="40">
         <v>1.1979166666666701</v>
       </c>
-      <c r="AD1" s="41">
+      <c r="AD1" s="38">
         <v>1.2083333333333399</v>
       </c>
-      <c r="AE1" s="42">
+      <c r="AE1" s="39">
         <v>1.21875</v>
       </c>
-      <c r="AF1" s="42">
+      <c r="AF1" s="39">
         <v>1.2291666666666701</v>
       </c>
-      <c r="AG1" s="43">
+      <c r="AG1" s="40">
         <v>1.2395833333333399</v>
       </c>
-      <c r="AH1" s="41">
+      <c r="AH1" s="38">
         <v>1.25</v>
       </c>
-      <c r="AI1" s="42">
+      <c r="AI1" s="39">
         <v>1.2604166666666701</v>
       </c>
-      <c r="AJ1" s="42">
+      <c r="AJ1" s="39">
         <v>1.2708333333333399</v>
       </c>
-      <c r="AK1" s="43">
+      <c r="AK1" s="40">
         <v>1.28125</v>
       </c>
-      <c r="AL1" s="41">
+      <c r="AL1" s="38">
         <v>1.2916666666666701</v>
       </c>
-      <c r="AM1" s="42">
+      <c r="AM1" s="39">
         <v>1.3020833333333399</v>
       </c>
-      <c r="AN1" s="42">
+      <c r="AN1" s="39">
         <v>1.3125</v>
       </c>
-      <c r="AO1" s="43">
+      <c r="AO1" s="40">
         <v>1.3229166666666701</v>
       </c>
-      <c r="AP1" s="41">
+      <c r="AP1" s="38">
         <v>1.3333333333333399</v>
       </c>
-      <c r="AQ1" s="42">
+      <c r="AQ1" s="39">
         <v>1.34375</v>
       </c>
-      <c r="AR1" s="42">
+      <c r="AR1" s="39">
         <v>1.3541666666666701</v>
       </c>
-      <c r="AS1" s="43">
+      <c r="AS1" s="40">
         <v>1.3645833333333399</v>
       </c>
-      <c r="AT1" s="41">
+      <c r="AT1" s="38">
         <v>1.375</v>
       </c>
-      <c r="AU1" s="42">
+      <c r="AU1" s="39">
         <v>1.3854166666666701</v>
       </c>
-      <c r="AV1" s="42">
+      <c r="AV1" s="39">
         <v>1.3958333333333399</v>
       </c>
-      <c r="AW1" s="43">
+      <c r="AW1" s="40">
         <v>1.40625</v>
       </c>
     </row>
     <row r="2" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="38"/>
-      <c r="AS2" s="38"/>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
+      <c r="A2" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -22983,7 +20943,7 @@
       </c>
     </row>
     <row r="9" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="30">
@@ -23180,7 +21140,7 @@
       </c>
     </row>
     <row r="10" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="30">
@@ -23377,7 +21337,7 @@
       </c>
     </row>
     <row r="11" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
@@ -23574,59 +21534,59 @@
       </c>
     </row>
     <row r="12" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="38"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="38"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="38"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="38"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="38"/>
-      <c r="AS12" s="38"/>
-      <c r="AT12" s="38"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="38"/>
-      <c r="AW12" s="39"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="43"/>
+      <c r="AF12" s="43"/>
+      <c r="AG12" s="43"/>
+      <c r="AH12" s="43"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="43"/>
+      <c r="AL12" s="43"/>
+      <c r="AM12" s="43"/>
+      <c r="AN12" s="43"/>
+      <c r="AO12" s="43"/>
+      <c r="AP12" s="43"/>
+      <c r="AQ12" s="43"/>
+      <c r="AR12" s="43"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="43"/>
+      <c r="AV12" s="43"/>
+      <c r="AW12" s="44"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>4</v>
       </c>
@@ -23702,8 +21662,8 @@
       <c r="AW13" s="22"/>
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>40</v>
+      <c r="A14" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="19"/>
@@ -23981,7 +21941,7 @@
       <c r="AW18" s="27"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="37" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="30">
@@ -24178,7 +22138,7 @@
       </c>
     </row>
     <row r="20" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="30">
@@ -24375,7 +22335,7 @@
       </c>
     </row>
     <row r="21" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="28" t="str">
@@ -24774,40 +22734,40 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"AL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Acar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"AL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"Acar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"AL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"Acar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"AL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"Acar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
       <formula>"AL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
       <formula>"Acar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
       <formula>"AL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"Acar6"</formula>
     </cfRule>
   </conditionalFormatting>
